--- a/helpers/exports/Rashid-slots-21-10-2024.xlsx
+++ b/helpers/exports/Rashid-slots-21-10-2024.xlsx
@@ -482,7 +482,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
         <v>9</v>
@@ -508,7 +508,7 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
         <v>9</v>
@@ -534,7 +534,7 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
         <v>9</v>
@@ -560,7 +560,7 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
         <v>9</v>
@@ -586,7 +586,7 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s">
         <v>9</v>
@@ -612,7 +612,7 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D7" t="s">
         <v>9</v>
@@ -638,7 +638,7 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D8" t="s">
         <v>9</v>
@@ -664,7 +664,7 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
         <v>9</v>
@@ -690,7 +690,7 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D10" t="s">
         <v>9</v>
@@ -716,7 +716,7 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" t="s">
         <v>9</v>
